--- a/artfynd/A 1695-2022 artfynd.xlsx
+++ b/artfynd/A 1695-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1695-2022 artfynd.xlsx
+++ b/artfynd/A 1695-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2192,7 +2192,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102578630</v>
+        <v>102577461</v>
       </c>
       <c r="B15" t="n">
         <v>96334</v>
@@ -2226,11 +2226,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2238,10 +2234,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568943.5187006677</v>
+        <v>568840.7178244028</v>
       </c>
       <c r="R15" t="n">
-        <v>6675292.634097782</v>
+        <v>6675277.274128784</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2273,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2283,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,7 +2306,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102577461</v>
+        <v>102578712</v>
       </c>
       <c r="B16" t="n">
         <v>96334</v>
@@ -2343,7 +2339,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2352,10 +2357,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568840.7178244028</v>
+        <v>568882.3364469918</v>
       </c>
       <c r="R16" t="n">
-        <v>6675277.274128784</v>
+        <v>6675235.795772789</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2387,7 +2392,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2397,7 +2402,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2424,7 +2429,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102578712</v>
+        <v>102578603</v>
       </c>
       <c r="B17" t="n">
         <v>96334</v>
@@ -2457,16 +2462,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2475,10 +2471,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>568882.3364469918</v>
+        <v>568919.4724653666</v>
       </c>
       <c r="R17" t="n">
-        <v>6675235.795772789</v>
+        <v>6675300.136102259</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2510,7 +2506,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,7 +2516,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,7 +2543,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102578603</v>
+        <v>102578454</v>
       </c>
       <c r="B18" t="n">
         <v>96334</v>
@@ -2580,8 +2576,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2589,10 +2598,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568919.4724653666</v>
+        <v>568814.9748903356</v>
       </c>
       <c r="R18" t="n">
-        <v>6675300.136102259</v>
+        <v>6675322.034150464</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2624,7 +2633,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2634,7 +2643,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,7 +2670,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102578454</v>
+        <v>102578432</v>
       </c>
       <c r="B19" t="n">
         <v>96334</v>
@@ -2694,21 +2703,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2716,10 +2712,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568814.9748903356</v>
+        <v>568796.1623448842</v>
       </c>
       <c r="R19" t="n">
-        <v>6675322.034150464</v>
+        <v>6675342.562146229</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2751,7 +2747,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2761,7 +2757,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2788,7 +2784,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102578432</v>
+        <v>102577567</v>
       </c>
       <c r="B20" t="n">
         <v>96334</v>
@@ -2830,10 +2826,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568796.1623448842</v>
+        <v>568740.0843670582</v>
       </c>
       <c r="R20" t="n">
-        <v>6675342.562146229</v>
+        <v>6675332.061551731</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2865,7 +2861,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,7 +2871,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,7 +2898,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102577567</v>
+        <v>102577581</v>
       </c>
       <c r="B21" t="n">
         <v>96334</v>
@@ -2936,7 +2932,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568740.0843670582</v>
+        <v>568709.1251434349</v>
       </c>
       <c r="R21" t="n">
-        <v>6675332.061551731</v>
+        <v>6675336.451838799</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3016,7 +3016,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102577581</v>
+        <v>102577558</v>
       </c>
       <c r="B22" t="n">
         <v>96334</v>
@@ -3050,11 +3050,7 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3062,10 +3058,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568709.1251434349</v>
+        <v>568745.1561249831</v>
       </c>
       <c r="R22" t="n">
-        <v>6675336.451838799</v>
+        <v>6675327.184991073</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3097,7 +3093,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3107,7 +3103,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3134,7 +3130,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102577558</v>
+        <v>102577453</v>
       </c>
       <c r="B23" t="n">
         <v>96334</v>
@@ -3168,7 +3164,11 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568745.1561249831</v>
+        <v>568849.9970305208</v>
       </c>
       <c r="R23" t="n">
-        <v>6675327.184991073</v>
+        <v>6675260.544123514</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3248,7 +3248,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102577453</v>
+        <v>102578427</v>
       </c>
       <c r="B24" t="n">
         <v>96334</v>
@@ -3281,12 +3281,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3294,10 +3299,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568849.9970305208</v>
+        <v>568780.7668224431</v>
       </c>
       <c r="R24" t="n">
-        <v>6675260.544123514</v>
+        <v>6675340.283937149</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3329,7 +3334,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3339,7 +3344,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,7 +3371,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102578547</v>
+        <v>102577546</v>
       </c>
       <c r="B25" t="n">
         <v>96334</v>
@@ -3408,10 +3413,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568913.8761624593</v>
+        <v>568771.5761971577</v>
       </c>
       <c r="R25" t="n">
-        <v>6675332.845128518</v>
+        <v>6675299.341807974</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3443,7 +3448,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3453,7 +3458,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3477,243 +3482,6 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>102578427</v>
-      </c>
-      <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Avesta, Dlr</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>568780.7668224431</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6675340.283937149</v>
-      </c>
-      <c r="S26" t="n">
-        <v>25</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Avesta</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Folkärna</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2022-07-31</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2022-07-31</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>102577546</v>
-      </c>
-      <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Avesta, Dlr</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>568771.5761971577</v>
-      </c>
-      <c r="R27" t="n">
-        <v>6675299.341807974</v>
-      </c>
-      <c r="S27" t="n">
-        <v>25</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Avesta</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Folkärna</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2022-07-31</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>07:52</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2022-07-31</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>07:52</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1695-2022 artfynd.xlsx
+++ b/artfynd/A 1695-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>102577450</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568865.918766204</v>
+        <v>568866</v>
       </c>
       <c r="R2" t="n">
-        <v>6675261.340978309</v>
+        <v>6675261</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -798,15 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102577481</v>
+        <v>102577453</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,7 +822,11 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568825.8572937254</v>
+        <v>568849</v>
       </c>
       <c r="R3" t="n">
-        <v>6675273.016991893</v>
+        <v>6675261</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102578555</v>
+        <v>102577461</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,16 +934,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -963,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568914.8718361049</v>
+        <v>568841</v>
       </c>
       <c r="R4" t="n">
-        <v>6675332.863883689</v>
+        <v>6675277</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,15 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102578523</v>
+        <v>102577465</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1043,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1077,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568868.6143820512</v>
+        <v>568837</v>
       </c>
       <c r="R5" t="n">
-        <v>6675382.705473591</v>
+        <v>6675274</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1112,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,15 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102578492</v>
+        <v>102577481</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568830.7115992124</v>
+        <v>568826</v>
       </c>
       <c r="R6" t="n">
-        <v>6675359.121855528</v>
+        <v>6675273</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,15 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102578613</v>
+        <v>102577530</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,12 +1270,12 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1309,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568914.9247053695</v>
+        <v>568743</v>
       </c>
       <c r="R7" t="n">
-        <v>6675277.179588424</v>
+        <v>6675253</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,7 +1308,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Folkärna</t>
+          <t>Grytnäs</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1344,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,15 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102578579</v>
+        <v>102577546</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568858.0342435325</v>
+        <v>568772</v>
       </c>
       <c r="R8" t="n">
-        <v>6675336.268359486</v>
+        <v>6675299</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1458,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,15 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102578424</v>
+        <v>102577558</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568780.8041979112</v>
+        <v>568745</v>
       </c>
       <c r="R9" t="n">
-        <v>6675338.295901154</v>
+        <v>6675327</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1572,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,7 +1546,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,15 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102578651</v>
+        <v>102577567</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568943.5374325406</v>
+        <v>568740</v>
       </c>
       <c r="R10" t="n">
-        <v>6675291.640066746</v>
+        <v>6675332</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1686,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,15 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102578590</v>
+        <v>102577573</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568902.6658022115</v>
+        <v>568742</v>
       </c>
       <c r="R11" t="n">
-        <v>6675267.004804974</v>
+        <v>6675334</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1800,7 +1754,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1764,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,15 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102577573</v>
+        <v>102577581</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1820,11 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1879,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568741.0426867655</v>
+        <v>568709</v>
       </c>
       <c r="R12" t="n">
-        <v>6675334.068298832</v>
+        <v>6675337</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1914,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,15 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102577465</v>
+        <v>102578255</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,16 +1932,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -2002,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568837.7868677597</v>
+        <v>568771</v>
       </c>
       <c r="R13" t="n">
-        <v>6675274.235818999</v>
+        <v>6675423</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2037,7 +1976,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,7 +1986,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,15 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102577530</v>
+        <v>102578424</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,11 +2041,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2120,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568743.0627151034</v>
+        <v>568781</v>
       </c>
       <c r="R14" t="n">
-        <v>6675253.064182248</v>
+        <v>6675338</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2145,7 +2075,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Grytnäs</t>
+          <t>Folkärna</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2155,7 +2085,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,7 +2095,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,15 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102577461</v>
+        <v>102578427</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2150,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2234,10 +2168,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568840.7178244028</v>
+        <v>568781</v>
       </c>
       <c r="R15" t="n">
-        <v>6675277.274128784</v>
+        <v>6675341</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2269,7 +2203,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2213,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,15 +2240,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102578712</v>
+        <v>102578432</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,16 +2268,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2357,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568882.3364469918</v>
+        <v>568796</v>
       </c>
       <c r="R16" t="n">
-        <v>6675235.795772789</v>
+        <v>6675343</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2392,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2402,7 +2322,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,15 +2349,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102578603</v>
+        <v>102578454</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,8 +2377,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2471,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>568919.4724653666</v>
+        <v>568815</v>
       </c>
       <c r="R17" t="n">
-        <v>6675300.136102259</v>
+        <v>6675322</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2506,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2516,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,15 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102578454</v>
+        <v>102578492</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2576,21 +2499,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2598,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568814.9748903356</v>
+        <v>568831</v>
       </c>
       <c r="R18" t="n">
-        <v>6675322.034150464</v>
+        <v>6675359</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2633,7 +2543,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2643,7 +2553,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2670,15 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102578432</v>
+        <v>102578523</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,10 +2617,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568796.1623448842</v>
+        <v>568869</v>
       </c>
       <c r="R19" t="n">
-        <v>6675342.562146229</v>
+        <v>6675383</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2747,7 +2652,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2757,7 +2662,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2784,15 +2689,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102577567</v>
+        <v>102578547</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2826,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568740.0843670582</v>
+        <v>568914</v>
       </c>
       <c r="R20" t="n">
-        <v>6675332.061551731</v>
+        <v>6675333</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2861,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2871,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,15 +2798,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102577581</v>
+        <v>102578555</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,12 +2826,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2944,10 +2844,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568709.1251434349</v>
+        <v>568915</v>
       </c>
       <c r="R21" t="n">
-        <v>6675336.451838799</v>
+        <v>6675333</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2979,7 +2879,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2989,7 +2889,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3016,15 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102577558</v>
+        <v>102578579</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568745.1561249831</v>
+        <v>568858</v>
       </c>
       <c r="R22" t="n">
-        <v>6675327.184991073</v>
+        <v>6675336</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3093,7 +2988,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3103,7 +2998,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3130,15 +3025,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102577453</v>
+        <v>102578590</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3164,11 +3054,7 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3176,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568849.9970305208</v>
+        <v>568903</v>
       </c>
       <c r="R23" t="n">
-        <v>6675260.544123514</v>
+        <v>6675267</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3211,7 +3097,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3221,7 +3107,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3248,15 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102578427</v>
+        <v>102578603</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,16 +3162,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3299,10 +3171,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568780.7668224431</v>
+        <v>568919</v>
       </c>
       <c r="R24" t="n">
-        <v>6675340.283937149</v>
+        <v>6675300</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3334,7 +3206,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3344,7 +3216,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3371,15 +3243,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102577546</v>
+        <v>102578613</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3405,7 +3272,11 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3413,10 +3284,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568771.5761971577</v>
+        <v>568914</v>
       </c>
       <c r="R25" t="n">
-        <v>6675299.341807974</v>
+        <v>6675277</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3448,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3458,7 +3329,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3482,6 +3353,346 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>102578630</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>568943</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6675293</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Folkärna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>102578651</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>568943</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6675292</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Folkärna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>102578712</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>568882</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6675235</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Folkärna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-07-31</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1695-2022 artfynd.xlsx
+++ b/artfynd/A 1695-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577450</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577453</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577461</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577465</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577481</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577530</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577546</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577558</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1679,6 +1724,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577567</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1788,6 +1838,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577573</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1901,6 +1956,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102577581</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2010,6 +2070,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578255</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2119,6 +2184,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578424</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2237,6 +2307,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578427</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2346,6 +2421,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578432</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2468,6 +2548,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578454</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2577,6 +2662,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578492</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2686,6 +2776,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578523</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2795,6 +2890,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578547</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2913,6 +3013,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578555</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3022,6 +3127,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578579</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3131,6 +3241,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578590</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3240,6 +3355,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578603</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3353,6 +3473,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578613</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3466,6 +3591,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578630</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3575,6 +3705,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578651</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3693,8 +3828,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102578712</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>